--- a/KAMCHATKA_ZAPOLNENIE/01_ООО_ЧелябинскСпецГражданСтрой_ЛД_Прайд.xlsx
+++ b/KAMCHATKA_ZAPOLNENIE/01_ООО_ЧелябинскСпецГражданСтрой_ЛД_Прайд.xlsx
@@ -925,7 +925,7 @@
       <c r="U6" s="7" t="n"/>
       <c r="V6" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЛД Прайд» (ИНН 7449114775)</t>
         </is>
       </c>
       <c r="W6" s="8" t="inlineStr">
@@ -933,8 +933,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X6" s="7" t="n"/>
-      <c r="Y6" s="7" t="n"/>
+      <c r="X6" s="8" t="inlineStr">
+        <is>
+          <t>10826766</t>
+        </is>
+      </c>
+      <c r="Y6" s="8" t="inlineStr">
+        <is>
+          <t>04.05.2031</t>
+        </is>
+      </c>
       <c r="Z6" s="7" t="n"/>
       <c r="AA6" s="9" t="n"/>
       <c r="AB6" s="10">
@@ -1041,7 +1049,7 @@
       <c r="U7" s="7" t="n"/>
       <c r="V7" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЛД Прайд» (ИНН 7449114775)</t>
         </is>
       </c>
       <c r="W7" s="8" t="inlineStr">
@@ -1049,8 +1057,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X7" s="7" t="n"/>
-      <c r="Y7" s="7" t="n"/>
+      <c r="X7" s="8" t="inlineStr">
+        <is>
+          <t>10826766</t>
+        </is>
+      </c>
+      <c r="Y7" s="8" t="inlineStr">
+        <is>
+          <t>04.05.2031</t>
+        </is>
+      </c>
       <c r="Z7" s="7" t="n"/>
       <c r="AA7" s="9" t="n"/>
       <c r="AB7" s="10">
@@ -1153,7 +1169,7 @@
       <c r="U8" s="7" t="n"/>
       <c r="V8" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЛД Прайд» (ИНН 7449114775)</t>
         </is>
       </c>
       <c r="W8" s="8" t="inlineStr">
@@ -1161,8 +1177,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X8" s="7" t="n"/>
-      <c r="Y8" s="7" t="n"/>
+      <c r="X8" s="8" t="inlineStr">
+        <is>
+          <t>10826766</t>
+        </is>
+      </c>
+      <c r="Y8" s="8" t="inlineStr">
+        <is>
+          <t>04.05.2031</t>
+        </is>
+      </c>
       <c r="Z8" s="7" t="n"/>
       <c r="AA8" s="9" t="n"/>
       <c r="AB8" s="10">
@@ -1269,7 +1293,7 @@
       <c r="U9" s="7" t="n"/>
       <c r="V9" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЛД Прайд» (ИНН 7449114775)</t>
         </is>
       </c>
       <c r="W9" s="8" t="inlineStr">
@@ -1277,8 +1301,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X9" s="7" t="n"/>
-      <c r="Y9" s="7" t="n"/>
+      <c r="X9" s="8" t="inlineStr">
+        <is>
+          <t>10826766</t>
+        </is>
+      </c>
+      <c r="Y9" s="8" t="inlineStr">
+        <is>
+          <t>04.05.2031</t>
+        </is>
+      </c>
       <c r="Z9" s="7" t="n"/>
       <c r="AA9" s="9" t="n"/>
       <c r="AB9" s="10">
@@ -1381,7 +1413,7 @@
       <c r="U10" s="7" t="n"/>
       <c r="V10" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЛД Прайд» (ИНН 7449114775)</t>
         </is>
       </c>
       <c r="W10" s="8" t="inlineStr">
@@ -1389,8 +1421,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X10" s="7" t="n"/>
-      <c r="Y10" s="7" t="n"/>
+      <c r="X10" s="8" t="inlineStr">
+        <is>
+          <t>10826766</t>
+        </is>
+      </c>
+      <c r="Y10" s="8" t="inlineStr">
+        <is>
+          <t>04.05.2031</t>
+        </is>
+      </c>
       <c r="Z10" s="7" t="n"/>
       <c r="AA10" s="9" t="n"/>
       <c r="AB10" s="10">
@@ -1497,7 +1537,7 @@
       <c r="U11" s="7" t="n"/>
       <c r="V11" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЛД Прайд» (ИНН 7449114775)</t>
         </is>
       </c>
       <c r="W11" s="8" t="inlineStr">
@@ -1505,8 +1545,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X11" s="7" t="n"/>
-      <c r="Y11" s="7" t="n"/>
+      <c r="X11" s="8" t="inlineStr">
+        <is>
+          <t>10826766</t>
+        </is>
+      </c>
+      <c r="Y11" s="8" t="inlineStr">
+        <is>
+          <t>04.05.2031</t>
+        </is>
+      </c>
       <c r="Z11" s="7" t="n"/>
       <c r="AA11" s="9" t="n"/>
       <c r="AB11" s="10">
@@ -1617,7 +1665,7 @@
       <c r="U12" s="7" t="n"/>
       <c r="V12" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W12" s="8" t="inlineStr">
@@ -1625,8 +1673,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X12" s="7" t="n"/>
-      <c r="Y12" s="7" t="n"/>
+      <c r="X12" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y12" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z12" s="7" t="n"/>
       <c r="AA12" s="9" t="n"/>
       <c r="AB12" s="10">
@@ -1735,7 +1791,7 @@
       <c r="U13" s="7" t="n"/>
       <c r="V13" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W13" s="8" t="inlineStr">
@@ -1743,8 +1799,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X13" s="7" t="n"/>
-      <c r="Y13" s="7" t="n"/>
+      <c r="X13" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y13" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z13" s="7" t="n"/>
       <c r="AA13" s="9" t="n"/>
       <c r="AB13" s="10">
@@ -1855,7 +1919,7 @@
       <c r="U14" s="7" t="n"/>
       <c r="V14" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W14" s="8" t="inlineStr">
@@ -1863,8 +1927,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X14" s="7" t="n"/>
-      <c r="Y14" s="7" t="n"/>
+      <c r="X14" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y14" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z14" s="7" t="n"/>
       <c r="AA14" s="9" t="n"/>
       <c r="AB14" s="10">
@@ -1971,7 +2043,7 @@
       <c r="U15" s="7" t="n"/>
       <c r="V15" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W15" s="8" t="inlineStr">
@@ -1979,8 +2051,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X15" s="7" t="n"/>
-      <c r="Y15" s="7" t="n"/>
+      <c r="X15" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y15" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z15" s="7" t="n"/>
       <c r="AA15" s="9" t="n"/>
       <c r="AB15" s="10">
@@ -2087,7 +2167,7 @@
       <c r="U16" s="7" t="n"/>
       <c r="V16" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W16" s="8" t="inlineStr">
@@ -2095,8 +2175,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X16" s="7" t="n"/>
-      <c r="Y16" s="7" t="n"/>
+      <c r="X16" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y16" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z16" s="7" t="n"/>
       <c r="AA16" s="9" t="n"/>
       <c r="AB16" s="10">
@@ -2203,7 +2291,7 @@
       <c r="U17" s="7" t="n"/>
       <c r="V17" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W17" s="8" t="inlineStr">
@@ -2211,8 +2299,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X17" s="7" t="n"/>
-      <c r="Y17" s="7" t="n"/>
+      <c r="X17" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y17" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z17" s="7" t="n"/>
       <c r="AA17" s="9" t="n"/>
       <c r="AB17" s="10">
@@ -2324,7 +2420,7 @@
       <c r="U18" s="7" t="n"/>
       <c r="V18" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W18" s="8" t="inlineStr">
@@ -2332,8 +2428,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X18" s="7" t="n"/>
-      <c r="Y18" s="7" t="n"/>
+      <c r="X18" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y18" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z18" s="7" t="n"/>
       <c r="AA18" s="9" t="n"/>
       <c r="AB18" s="10">
@@ -2440,7 +2544,7 @@
       <c r="U19" s="7" t="n"/>
       <c r="V19" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЛД Прайд» (ИНН 7449114775)</t>
         </is>
       </c>
       <c r="W19" s="8" t="inlineStr">
@@ -2448,8 +2552,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X19" s="7" t="n"/>
-      <c r="Y19" s="7" t="n"/>
+      <c r="X19" s="8" t="inlineStr">
+        <is>
+          <t>10826766</t>
+        </is>
+      </c>
+      <c r="Y19" s="8" t="inlineStr">
+        <is>
+          <t>04.05.2031</t>
+        </is>
+      </c>
       <c r="Z19" s="7" t="n"/>
       <c r="AA19" s="9" t="n"/>
       <c r="AB19" s="10">
@@ -2556,7 +2668,7 @@
       <c r="U20" s="7" t="n"/>
       <c r="V20" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЛД Прайд» (ИНН 7449114775)</t>
         </is>
       </c>
       <c r="W20" s="8" t="inlineStr">
@@ -2564,8 +2676,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X20" s="7" t="n"/>
-      <c r="Y20" s="7" t="n"/>
+      <c r="X20" s="8" t="inlineStr">
+        <is>
+          <t>10826766</t>
+        </is>
+      </c>
+      <c r="Y20" s="8" t="inlineStr">
+        <is>
+          <t>04.05.2031</t>
+        </is>
+      </c>
       <c r="Z20" s="7" t="n"/>
       <c r="AA20" s="9" t="n"/>
       <c r="AB20" s="10">
@@ -2668,7 +2788,7 @@
       <c r="U21" s="7" t="n"/>
       <c r="V21" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЛД Прайд» (ИНН 7449114775)</t>
         </is>
       </c>
       <c r="W21" s="8" t="inlineStr">
@@ -2676,8 +2796,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X21" s="7" t="n"/>
-      <c r="Y21" s="7" t="n"/>
+      <c r="X21" s="8" t="inlineStr">
+        <is>
+          <t>10826766</t>
+        </is>
+      </c>
+      <c r="Y21" s="8" t="inlineStr">
+        <is>
+          <t>04.05.2031</t>
+        </is>
+      </c>
       <c r="Z21" s="7" t="n"/>
       <c r="AA21" s="9" t="n"/>
       <c r="AB21" s="10">
@@ -2784,7 +2912,7 @@
       <c r="U22" s="7" t="n"/>
       <c r="V22" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЛД Прайд» (ИНН 7449114775)</t>
         </is>
       </c>
       <c r="W22" s="8" t="inlineStr">
@@ -2792,8 +2920,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X22" s="7" t="n"/>
-      <c r="Y22" s="7" t="n"/>
+      <c r="X22" s="8" t="inlineStr">
+        <is>
+          <t>10826766</t>
+        </is>
+      </c>
+      <c r="Y22" s="8" t="inlineStr">
+        <is>
+          <t>04.05.2031</t>
+        </is>
+      </c>
       <c r="Z22" s="7" t="n"/>
       <c r="AA22" s="9" t="n"/>
       <c r="AB22" s="10">
@@ -2900,7 +3036,7 @@
       <c r="U23" s="7" t="n"/>
       <c r="V23" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЛД Прайд» (ИНН 7449114775)</t>
         </is>
       </c>
       <c r="W23" s="8" t="inlineStr">
@@ -2908,8 +3044,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X23" s="7" t="n"/>
-      <c r="Y23" s="7" t="n"/>
+      <c r="X23" s="8" t="inlineStr">
+        <is>
+          <t>10826766</t>
+        </is>
+      </c>
+      <c r="Y23" s="8" t="inlineStr">
+        <is>
+          <t>04.05.2031</t>
+        </is>
+      </c>
       <c r="Z23" s="7" t="n"/>
       <c r="AA23" s="9" t="n"/>
       <c r="AB23" s="10">
@@ -3020,7 +3164,7 @@
       <c r="U24" s="7" t="n"/>
       <c r="V24" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W24" s="8" t="inlineStr">
@@ -3028,8 +3172,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X24" s="7" t="n"/>
-      <c r="Y24" s="7" t="n"/>
+      <c r="X24" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y24" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z24" s="7" t="n"/>
       <c r="AA24" s="9" t="n"/>
       <c r="AB24" s="10">
@@ -3140,7 +3292,7 @@
       <c r="U25" s="7" t="n"/>
       <c r="V25" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W25" s="8" t="inlineStr">
@@ -3148,8 +3300,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X25" s="7" t="n"/>
-      <c r="Y25" s="7" t="n"/>
+      <c r="X25" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y25" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z25" s="7" t="n"/>
       <c r="AA25" s="9" t="n"/>
       <c r="AB25" s="10">
@@ -3260,7 +3420,7 @@
       <c r="U26" s="7" t="n"/>
       <c r="V26" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W26" s="8" t="inlineStr">
@@ -3268,8 +3428,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X26" s="7" t="n"/>
-      <c r="Y26" s="7" t="n"/>
+      <c r="X26" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y26" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z26" s="7" t="n"/>
       <c r="AA26" s="9" t="n"/>
       <c r="AB26" s="10">
@@ -3376,7 +3544,7 @@
       <c r="U27" s="7" t="n"/>
       <c r="V27" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W27" s="8" t="inlineStr">
@@ -3384,8 +3552,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X27" s="7" t="n"/>
-      <c r="Y27" s="7" t="n"/>
+      <c r="X27" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y27" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z27" s="7" t="n"/>
       <c r="AA27" s="9" t="n"/>
       <c r="AB27" s="10">
@@ -3492,7 +3668,7 @@
       <c r="U28" s="7" t="n"/>
       <c r="V28" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W28" s="8" t="inlineStr">
@@ -3500,8 +3676,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X28" s="7" t="n"/>
-      <c r="Y28" s="7" t="n"/>
+      <c r="X28" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y28" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z28" s="7" t="n"/>
       <c r="AA28" s="9" t="n"/>
       <c r="AB28" s="10">
@@ -3608,7 +3792,7 @@
       <c r="U29" s="7" t="n"/>
       <c r="V29" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W29" s="8" t="inlineStr">
@@ -3616,8 +3800,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X29" s="7" t="n"/>
-      <c r="Y29" s="7" t="n"/>
+      <c r="X29" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y29" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z29" s="7" t="n"/>
       <c r="AA29" s="9" t="n"/>
       <c r="AB29" s="10">
@@ -3724,7 +3916,7 @@
       <c r="U30" s="7" t="n"/>
       <c r="V30" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W30" s="8" t="inlineStr">
@@ -3732,8 +3924,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X30" s="7" t="n"/>
-      <c r="Y30" s="7" t="n"/>
+      <c r="X30" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y30" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z30" s="7" t="n"/>
       <c r="AA30" s="9" t="n"/>
       <c r="AB30" s="10">
@@ -3839,7 +4039,7 @@
       <c r="U31" s="7" t="n"/>
       <c r="V31" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W31" s="8" t="inlineStr">
@@ -3847,8 +4047,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X31" s="7" t="n"/>
-      <c r="Y31" s="7" t="n"/>
+      <c r="X31" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y31" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z31" s="7" t="n"/>
       <c r="AA31" s="9" t="n"/>
       <c r="AB31" s="10">
@@ -3947,7 +4155,7 @@
       <c r="U32" s="7" t="n"/>
       <c r="V32" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W32" s="8" t="inlineStr">
@@ -3955,8 +4163,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X32" s="7" t="n"/>
-      <c r="Y32" s="7" t="n"/>
+      <c r="X32" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y32" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z32" s="7" t="n"/>
       <c r="AA32" s="9" t="n"/>
       <c r="AB32" s="10">
@@ -4063,7 +4279,7 @@
       <c r="U33" s="7" t="n"/>
       <c r="V33" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W33" s="8" t="inlineStr">
@@ -4071,8 +4287,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X33" s="7" t="n"/>
-      <c r="Y33" s="7" t="n"/>
+      <c r="X33" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y33" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z33" s="7" t="n"/>
       <c r="AA33" s="9" t="n"/>
       <c r="AB33" s="10">
@@ -4178,7 +4402,7 @@
       <c r="U34" s="7" t="n"/>
       <c r="V34" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W34" s="8" t="inlineStr">
@@ -4186,8 +4410,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X34" s="7" t="n"/>
-      <c r="Y34" s="7" t="n"/>
+      <c r="X34" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y34" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z34" s="7" t="n"/>
       <c r="AA34" s="9" t="n"/>
       <c r="AB34" s="10">
@@ -4294,7 +4526,7 @@
       <c r="U35" s="7" t="n"/>
       <c r="V35" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W35" s="8" t="inlineStr">
@@ -4302,8 +4534,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X35" s="7" t="n"/>
-      <c r="Y35" s="7" t="n"/>
+      <c r="X35" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y35" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z35" s="7" t="n"/>
       <c r="AA35" s="9" t="n"/>
       <c r="AB35" s="10">
@@ -4410,7 +4650,7 @@
       <c r="U36" s="7" t="n"/>
       <c r="V36" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W36" s="8" t="inlineStr">
@@ -4418,8 +4658,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X36" s="7" t="n"/>
-      <c r="Y36" s="7" t="n"/>
+      <c r="X36" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y36" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z36" s="7" t="n"/>
       <c r="AA36" s="9" t="n"/>
       <c r="AB36" s="10">
@@ -4526,7 +4774,7 @@
       <c r="U37" s="7" t="n"/>
       <c r="V37" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W37" s="8" t="inlineStr">
@@ -4534,8 +4782,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X37" s="7" t="n"/>
-      <c r="Y37" s="7" t="n"/>
+      <c r="X37" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y37" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z37" s="7" t="n"/>
       <c r="AA37" s="9" t="n"/>
       <c r="AB37" s="10">
@@ -4642,7 +4898,7 @@
       <c r="U38" s="7" t="n"/>
       <c r="V38" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W38" s="8" t="inlineStr">
@@ -4650,8 +4906,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X38" s="7" t="n"/>
-      <c r="Y38" s="7" t="n"/>
+      <c r="X38" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y38" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z38" s="7" t="n"/>
       <c r="AA38" s="9" t="n"/>
       <c r="AB38" s="10">
@@ -4758,7 +5022,7 @@
       <c r="U39" s="7" t="n"/>
       <c r="V39" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W39" s="8" t="inlineStr">
@@ -4766,8 +5030,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X39" s="7" t="n"/>
-      <c r="Y39" s="7" t="n"/>
+      <c r="X39" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y39" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z39" s="7" t="n"/>
       <c r="AA39" s="9" t="n"/>
       <c r="AB39" s="10">
@@ -4874,7 +5146,7 @@
       <c r="U40" s="7" t="n"/>
       <c r="V40" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W40" s="8" t="inlineStr">
@@ -4882,8 +5154,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X40" s="7" t="n"/>
-      <c r="Y40" s="7" t="n"/>
+      <c r="X40" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y40" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z40" s="7" t="n"/>
       <c r="AA40" s="9" t="n"/>
       <c r="AB40" s="10">
@@ -4990,7 +5270,7 @@
       <c r="U41" s="7" t="n"/>
       <c r="V41" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W41" s="8" t="inlineStr">
@@ -4998,8 +5278,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X41" s="7" t="n"/>
-      <c r="Y41" s="7" t="n"/>
+      <c r="X41" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y41" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z41" s="7" t="n"/>
       <c r="AA41" s="9" t="n"/>
       <c r="AB41" s="10">
@@ -5106,7 +5394,7 @@
       <c r="U42" s="7" t="n"/>
       <c r="V42" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W42" s="8" t="inlineStr">
@@ -5114,8 +5402,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X42" s="7" t="n"/>
-      <c r="Y42" s="7" t="n"/>
+      <c r="X42" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y42" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z42" s="7" t="n"/>
       <c r="AA42" s="9" t="n"/>
       <c r="AB42" s="10">
@@ -5222,7 +5518,7 @@
       <c r="U43" s="7" t="n"/>
       <c r="V43" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W43" s="8" t="inlineStr">
@@ -5230,8 +5526,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X43" s="7" t="n"/>
-      <c r="Y43" s="7" t="n"/>
+      <c r="X43" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y43" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z43" s="7" t="n"/>
       <c r="AA43" s="9" t="n"/>
       <c r="AB43" s="10">
@@ -5338,7 +5642,7 @@
       <c r="U44" s="7" t="n"/>
       <c r="V44" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W44" s="8" t="inlineStr">
@@ -5346,8 +5650,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X44" s="7" t="n"/>
-      <c r="Y44" s="7" t="n"/>
+      <c r="X44" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y44" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z44" s="7" t="n"/>
       <c r="AA44" s="9" t="n"/>
       <c r="AB44" s="10">
@@ -5459,7 +5771,7 @@
       <c r="U45" s="7" t="n"/>
       <c r="V45" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W45" s="8" t="inlineStr">
@@ -5467,8 +5779,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X45" s="7" t="n"/>
-      <c r="Y45" s="7" t="n"/>
+      <c r="X45" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y45" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z45" s="7" t="n"/>
       <c r="AA45" s="9" t="n"/>
       <c r="AB45" s="10">
@@ -5580,7 +5900,7 @@
       <c r="U46" s="7" t="n"/>
       <c r="V46" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W46" s="8" t="inlineStr">
@@ -5588,8 +5908,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X46" s="7" t="n"/>
-      <c r="Y46" s="7" t="n"/>
+      <c r="X46" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y46" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z46" s="7" t="n"/>
       <c r="AA46" s="9" t="n"/>
       <c r="AB46" s="10">
@@ -5701,7 +6029,7 @@
       <c r="U47" s="7" t="n"/>
       <c r="V47" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W47" s="8" t="inlineStr">
@@ -5709,8 +6037,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X47" s="7" t="n"/>
-      <c r="Y47" s="7" t="n"/>
+      <c r="X47" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y47" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z47" s="7" t="n"/>
       <c r="AA47" s="9" t="n"/>
       <c r="AB47" s="10">
@@ -5822,7 +6158,7 @@
       <c r="U48" s="7" t="n"/>
       <c r="V48" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W48" s="8" t="inlineStr">
@@ -5830,8 +6166,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X48" s="7" t="n"/>
-      <c r="Y48" s="7" t="n"/>
+      <c r="X48" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y48" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z48" s="7" t="n"/>
       <c r="AA48" s="9" t="n"/>
       <c r="AB48" s="10">
@@ -5934,7 +6278,7 @@
       <c r="U49" s="7" t="n"/>
       <c r="V49" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W49" s="8" t="inlineStr">
@@ -5942,8 +6286,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X49" s="7" t="n"/>
-      <c r="Y49" s="7" t="n"/>
+      <c r="X49" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y49" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z49" s="7" t="n"/>
       <c r="AA49" s="9" t="n"/>
       <c r="AB49" s="10">
@@ -6046,7 +6398,7 @@
       <c r="U50" s="7" t="n"/>
       <c r="V50" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W50" s="8" t="inlineStr">
@@ -6054,8 +6406,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X50" s="7" t="n"/>
-      <c r="Y50" s="7" t="n"/>
+      <c r="X50" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y50" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z50" s="7" t="n"/>
       <c r="AA50" s="9" t="n"/>
       <c r="AB50" s="10">
@@ -6158,7 +6518,7 @@
       <c r="U51" s="7" t="n"/>
       <c r="V51" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W51" s="8" t="inlineStr">
@@ -6166,8 +6526,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X51" s="7" t="n"/>
-      <c r="Y51" s="7" t="n"/>
+      <c r="X51" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y51" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z51" s="7" t="n"/>
       <c r="AA51" s="9" t="n"/>
       <c r="AB51" s="10">
@@ -6270,7 +6638,7 @@
       <c r="U52" s="7" t="n"/>
       <c r="V52" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W52" s="8" t="inlineStr">
@@ -6278,8 +6646,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X52" s="7" t="n"/>
-      <c r="Y52" s="7" t="n"/>
+      <c r="X52" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y52" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z52" s="7" t="n"/>
       <c r="AA52" s="9" t="n"/>
       <c r="AB52" s="10">
@@ -6382,7 +6758,7 @@
       <c r="U53" s="7" t="n"/>
       <c r="V53" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W53" s="8" t="inlineStr">
@@ -6390,8 +6766,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X53" s="7" t="n"/>
-      <c r="Y53" s="7" t="n"/>
+      <c r="X53" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y53" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z53" s="7" t="n"/>
       <c r="AA53" s="9" t="n"/>
       <c r="AB53" s="10">
@@ -6498,7 +6882,7 @@
       <c r="U54" s="7" t="n"/>
       <c r="V54" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W54" s="8" t="inlineStr">
@@ -6506,8 +6890,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X54" s="7" t="n"/>
-      <c r="Y54" s="7" t="n"/>
+      <c r="X54" s="8" t="inlineStr">
+        <is>
+          <t>10714005</t>
+        </is>
+      </c>
+      <c r="Y54" s="8" t="inlineStr">
+        <is>
+          <t>17.09.2028</t>
+        </is>
+      </c>
       <c r="Z54" s="7" t="n"/>
       <c r="AA54" s="9" t="n"/>
       <c r="AB54" s="10">
@@ -6614,7 +7006,7 @@
       <c r="U55" s="7" t="n"/>
       <c r="V55" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W55" s="8" t="inlineStr">
@@ -6622,8 +7014,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X55" s="7" t="n"/>
-      <c r="Y55" s="7" t="n"/>
+      <c r="X55" s="8" t="inlineStr">
+        <is>
+          <t>10714005</t>
+        </is>
+      </c>
+      <c r="Y55" s="8" t="inlineStr">
+        <is>
+          <t>17.09.2028</t>
+        </is>
+      </c>
       <c r="Z55" s="7" t="n"/>
       <c r="AA55" s="9" t="n"/>
       <c r="AB55" s="10">
@@ -6730,7 +7130,7 @@
       <c r="U56" s="7" t="n"/>
       <c r="V56" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W56" s="8" t="inlineStr">
@@ -6738,8 +7138,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X56" s="7" t="n"/>
-      <c r="Y56" s="7" t="n"/>
+      <c r="X56" s="8" t="inlineStr">
+        <is>
+          <t>10714005</t>
+        </is>
+      </c>
+      <c r="Y56" s="8" t="inlineStr">
+        <is>
+          <t>17.09.2028</t>
+        </is>
+      </c>
       <c r="Z56" s="7" t="n"/>
       <c r="AA56" s="9" t="n"/>
       <c r="AB56" s="10">
@@ -6842,7 +7250,7 @@
       <c r="U57" s="7" t="n"/>
       <c r="V57" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W57" s="8" t="inlineStr">
@@ -6850,8 +7258,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X57" s="7" t="n"/>
-      <c r="Y57" s="7" t="n"/>
+      <c r="X57" s="8" t="inlineStr">
+        <is>
+          <t>10714005</t>
+        </is>
+      </c>
+      <c r="Y57" s="8" t="inlineStr">
+        <is>
+          <t>17.09.2028</t>
+        </is>
+      </c>
       <c r="Z57" s="7" t="n"/>
       <c r="AA57" s="9" t="n"/>
       <c r="AB57" s="10">
@@ -6954,7 +7370,7 @@
       <c r="U58" s="7" t="n"/>
       <c r="V58" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W58" s="8" t="inlineStr">
@@ -6962,8 +7378,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X58" s="7" t="n"/>
-      <c r="Y58" s="7" t="n"/>
+      <c r="X58" s="8" t="inlineStr">
+        <is>
+          <t>10714005</t>
+        </is>
+      </c>
+      <c r="Y58" s="8" t="inlineStr">
+        <is>
+          <t>17.09.2028</t>
+        </is>
+      </c>
       <c r="Z58" s="7" t="n"/>
       <c r="AA58" s="9" t="n"/>
       <c r="AB58" s="10">
@@ -7066,7 +7490,7 @@
       <c r="U59" s="7" t="n"/>
       <c r="V59" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W59" s="8" t="inlineStr">
@@ -7074,8 +7498,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X59" s="7" t="n"/>
-      <c r="Y59" s="7" t="n"/>
+      <c r="X59" s="8" t="inlineStr">
+        <is>
+          <t>10714005</t>
+        </is>
+      </c>
+      <c r="Y59" s="8" t="inlineStr">
+        <is>
+          <t>17.09.2028</t>
+        </is>
+      </c>
       <c r="Z59" s="7" t="n"/>
       <c r="AA59" s="9" t="n"/>
       <c r="AB59" s="10">
@@ -7178,7 +7610,7 @@
       <c r="U60" s="7" t="n"/>
       <c r="V60" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W60" s="8" t="inlineStr">
@@ -7186,8 +7618,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X60" s="7" t="n"/>
-      <c r="Y60" s="7" t="n"/>
+      <c r="X60" s="8" t="inlineStr">
+        <is>
+          <t>10714005</t>
+        </is>
+      </c>
+      <c r="Y60" s="8" t="inlineStr">
+        <is>
+          <t>17.09.2028</t>
+        </is>
+      </c>
       <c r="Z60" s="7" t="n"/>
       <c r="AA60" s="9" t="n"/>
       <c r="AB60" s="10">
@@ -7290,7 +7730,7 @@
       <c r="U61" s="7" t="n"/>
       <c r="V61" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W61" s="8" t="inlineStr">
@@ -7298,8 +7738,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X61" s="7" t="n"/>
-      <c r="Y61" s="7" t="n"/>
+      <c r="X61" s="8" t="inlineStr">
+        <is>
+          <t>10714005</t>
+        </is>
+      </c>
+      <c r="Y61" s="8" t="inlineStr">
+        <is>
+          <t>17.09.2028</t>
+        </is>
+      </c>
       <c r="Z61" s="7" t="n"/>
       <c r="AA61" s="9" t="n"/>
       <c r="AB61" s="10">
@@ -7402,7 +7850,7 @@
       <c r="U62" s="7" t="n"/>
       <c r="V62" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W62" s="8" t="inlineStr">
@@ -7410,8 +7858,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X62" s="7" t="n"/>
-      <c r="Y62" s="7" t="n"/>
+      <c r="X62" s="8" t="inlineStr">
+        <is>
+          <t>10714005</t>
+        </is>
+      </c>
+      <c r="Y62" s="8" t="inlineStr">
+        <is>
+          <t>17.09.2028</t>
+        </is>
+      </c>
       <c r="Z62" s="7" t="n"/>
       <c r="AA62" s="9" t="n"/>
       <c r="AB62" s="10">
@@ -7742,7 +8198,7 @@
       <c r="U65" s="7" t="n"/>
       <c r="V65" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W65" s="8" t="inlineStr">
@@ -7750,8 +8206,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X65" s="7" t="n"/>
-      <c r="Y65" s="7" t="n"/>
+      <c r="X65" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y65" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z65" s="7" t="n"/>
       <c r="AA65" s="9" t="n"/>
       <c r="AB65" s="10">
@@ -7858,7 +8322,7 @@
       <c r="U66" s="7" t="n"/>
       <c r="V66" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЛД Прайд» (ИНН 7449114775)</t>
         </is>
       </c>
       <c r="W66" s="8" t="inlineStr">
@@ -7866,8 +8330,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X66" s="7" t="n"/>
-      <c r="Y66" s="7" t="n"/>
+      <c r="X66" s="8" t="inlineStr">
+        <is>
+          <t>10826766</t>
+        </is>
+      </c>
+      <c r="Y66" s="8" t="inlineStr">
+        <is>
+          <t>04.05.2031</t>
+        </is>
+      </c>
       <c r="Z66" s="7" t="n"/>
       <c r="AA66" s="9" t="n"/>
       <c r="AB66" s="10">
@@ -7978,7 +8450,7 @@
       <c r="U67" s="7" t="n"/>
       <c r="V67" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЛД Прайд» (ИНН 7449114775)</t>
         </is>
       </c>
       <c r="W67" s="8" t="inlineStr">
@@ -7986,8 +8458,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X67" s="7" t="n"/>
-      <c r="Y67" s="7" t="n"/>
+      <c r="X67" s="8" t="inlineStr">
+        <is>
+          <t>10826766</t>
+        </is>
+      </c>
+      <c r="Y67" s="8" t="inlineStr">
+        <is>
+          <t>04.05.2031</t>
+        </is>
+      </c>
       <c r="Z67" s="7" t="n"/>
       <c r="AA67" s="9" t="n"/>
       <c r="AB67" s="10">
@@ -8090,7 +8570,7 @@
       <c r="U68" s="7" t="n"/>
       <c r="V68" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЛД Прайд» (ИНН 7449114775)</t>
         </is>
       </c>
       <c r="W68" s="8" t="inlineStr">
@@ -8098,8 +8578,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X68" s="7" t="n"/>
-      <c r="Y68" s="7" t="n"/>
+      <c r="X68" s="8" t="inlineStr">
+        <is>
+          <t>10826766</t>
+        </is>
+      </c>
+      <c r="Y68" s="8" t="inlineStr">
+        <is>
+          <t>04.05.2031</t>
+        </is>
+      </c>
       <c r="Z68" s="7" t="n"/>
       <c r="AA68" s="9" t="n"/>
       <c r="AB68" s="10">
@@ -8206,7 +8694,7 @@
       <c r="U69" s="7" t="n"/>
       <c r="V69" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЛД Прайд» (ИНН 7449114775)</t>
         </is>
       </c>
       <c r="W69" s="8" t="inlineStr">
@@ -8214,8 +8702,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X69" s="7" t="n"/>
-      <c r="Y69" s="7" t="n"/>
+      <c r="X69" s="8" t="inlineStr">
+        <is>
+          <t>10826766</t>
+        </is>
+      </c>
+      <c r="Y69" s="8" t="inlineStr">
+        <is>
+          <t>04.05.2031</t>
+        </is>
+      </c>
       <c r="Z69" s="7" t="n"/>
       <c r="AA69" s="9" t="n"/>
       <c r="AB69" s="10">
@@ -8322,7 +8818,7 @@
       <c r="U70" s="7" t="n"/>
       <c r="V70" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЛД Прайд» (ИНН 7449114775)</t>
         </is>
       </c>
       <c r="W70" s="8" t="inlineStr">
@@ -8330,8 +8826,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X70" s="7" t="n"/>
-      <c r="Y70" s="7" t="n"/>
+      <c r="X70" s="8" t="inlineStr">
+        <is>
+          <t>10826766</t>
+        </is>
+      </c>
+      <c r="Y70" s="8" t="inlineStr">
+        <is>
+          <t>04.05.2031</t>
+        </is>
+      </c>
       <c r="Z70" s="7" t="n"/>
       <c r="AA70" s="9" t="n"/>
       <c r="AB70" s="10">
@@ -8442,7 +8946,7 @@
       <c r="U71" s="7" t="n"/>
       <c r="V71" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W71" s="8" t="inlineStr">
@@ -8450,8 +8954,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X71" s="7" t="n"/>
-      <c r="Y71" s="7" t="n"/>
+      <c r="X71" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y71" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z71" s="7" t="n"/>
       <c r="AA71" s="9" t="n"/>
       <c r="AB71" s="10">
@@ -8562,7 +9074,7 @@
       <c r="U72" s="7" t="n"/>
       <c r="V72" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W72" s="8" t="inlineStr">
@@ -8570,8 +9082,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X72" s="7" t="n"/>
-      <c r="Y72" s="7" t="n"/>
+      <c r="X72" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y72" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z72" s="7" t="n"/>
       <c r="AA72" s="9" t="n"/>
       <c r="AB72" s="10">
@@ -8682,7 +9202,7 @@
       <c r="U73" s="7" t="n"/>
       <c r="V73" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W73" s="8" t="inlineStr">
@@ -8690,8 +9210,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X73" s="7" t="n"/>
-      <c r="Y73" s="7" t="n"/>
+      <c r="X73" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y73" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z73" s="7" t="n"/>
       <c r="AA73" s="9" t="n"/>
       <c r="AB73" s="10">
@@ -8797,7 +9325,7 @@
       <c r="U74" s="7" t="n"/>
       <c r="V74" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W74" s="8" t="inlineStr">
@@ -8805,8 +9333,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X74" s="7" t="n"/>
-      <c r="Y74" s="7" t="n"/>
+      <c r="X74" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y74" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z74" s="7" t="n"/>
       <c r="AA74" s="9" t="n"/>
       <c r="AB74" s="10">
@@ -8905,7 +9441,7 @@
       <c r="U75" s="7" t="n"/>
       <c r="V75" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W75" s="8" t="inlineStr">
@@ -8913,8 +9449,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X75" s="7" t="n"/>
-      <c r="Y75" s="7" t="n"/>
+      <c r="X75" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y75" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z75" s="7" t="n"/>
       <c r="AA75" s="9" t="n"/>
       <c r="AB75" s="10">
@@ -9021,7 +9565,7 @@
       <c r="U76" s="7" t="n"/>
       <c r="V76" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W76" s="8" t="inlineStr">
@@ -9029,8 +9573,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X76" s="7" t="n"/>
-      <c r="Y76" s="7" t="n"/>
+      <c r="X76" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y76" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z76" s="7" t="n"/>
       <c r="AA76" s="9" t="n"/>
       <c r="AB76" s="10">
@@ -9136,7 +9688,7 @@
       <c r="U77" s="7" t="n"/>
       <c r="V77" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W77" s="8" t="inlineStr">
@@ -9144,8 +9696,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X77" s="7" t="n"/>
-      <c r="Y77" s="7" t="n"/>
+      <c r="X77" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y77" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z77" s="7" t="n"/>
       <c r="AA77" s="9" t="n"/>
       <c r="AB77" s="10">
@@ -9252,7 +9812,7 @@
       <c r="U78" s="7" t="n"/>
       <c r="V78" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W78" s="8" t="inlineStr">
@@ -9260,8 +9820,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X78" s="7" t="n"/>
-      <c r="Y78" s="7" t="n"/>
+      <c r="X78" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y78" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z78" s="7" t="n"/>
       <c r="AA78" s="9" t="n"/>
       <c r="AB78" s="10">
@@ -9368,7 +9936,7 @@
       <c r="U79" s="7" t="n"/>
       <c r="V79" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W79" s="8" t="inlineStr">
@@ -9376,8 +9944,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X79" s="7" t="n"/>
-      <c r="Y79" s="7" t="n"/>
+      <c r="X79" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y79" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z79" s="7" t="n"/>
       <c r="AA79" s="9" t="n"/>
       <c r="AB79" s="10">
@@ -9484,7 +10060,7 @@
       <c r="U80" s="7" t="n"/>
       <c r="V80" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W80" s="8" t="inlineStr">
@@ -9492,8 +10068,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X80" s="7" t="n"/>
-      <c r="Y80" s="7" t="n"/>
+      <c r="X80" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y80" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z80" s="7" t="n"/>
       <c r="AA80" s="9" t="n"/>
       <c r="AB80" s="10">
@@ -9604,7 +10188,7 @@
       <c r="U81" s="7" t="n"/>
       <c r="V81" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЛД Прайд» (ИНН 7449114775)</t>
         </is>
       </c>
       <c r="W81" s="8" t="inlineStr">
@@ -9612,8 +10196,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X81" s="7" t="n"/>
-      <c r="Y81" s="7" t="n"/>
+      <c r="X81" s="8" t="inlineStr">
+        <is>
+          <t>10826766</t>
+        </is>
+      </c>
+      <c r="Y81" s="8" t="inlineStr">
+        <is>
+          <t>04.05.2031</t>
+        </is>
+      </c>
       <c r="Z81" s="7" t="n"/>
       <c r="AA81" s="9" t="n"/>
       <c r="AB81" s="10">
@@ -9724,7 +10316,7 @@
       <c r="U82" s="7" t="n"/>
       <c r="V82" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЛД Прайд» (ИНН 7449114775)</t>
         </is>
       </c>
       <c r="W82" s="8" t="inlineStr">
@@ -9732,8 +10324,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X82" s="7" t="n"/>
-      <c r="Y82" s="7" t="n"/>
+      <c r="X82" s="8" t="inlineStr">
+        <is>
+          <t>10826766</t>
+        </is>
+      </c>
+      <c r="Y82" s="8" t="inlineStr">
+        <is>
+          <t>04.05.2031</t>
+        </is>
+      </c>
       <c r="Z82" s="7" t="n"/>
       <c r="AA82" s="9" t="n"/>
       <c r="AB82" s="10">
@@ -9844,7 +10444,7 @@
       <c r="U83" s="7" t="n"/>
       <c r="V83" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЛД Прайд» (ИНН 7449114775)</t>
         </is>
       </c>
       <c r="W83" s="8" t="inlineStr">
@@ -9852,8 +10452,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X83" s="7" t="n"/>
-      <c r="Y83" s="7" t="n"/>
+      <c r="X83" s="8" t="inlineStr">
+        <is>
+          <t>10826766</t>
+        </is>
+      </c>
+      <c r="Y83" s="8" t="inlineStr">
+        <is>
+          <t>04.05.2031</t>
+        </is>
+      </c>
       <c r="Z83" s="7" t="n"/>
       <c r="AA83" s="9" t="n"/>
       <c r="AB83" s="10">
@@ -9964,7 +10572,7 @@
       <c r="U84" s="7" t="n"/>
       <c r="V84" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЛД Прайд» (ИНН 7449114775)</t>
         </is>
       </c>
       <c r="W84" s="8" t="inlineStr">
@@ -9972,8 +10580,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X84" s="7" t="n"/>
-      <c r="Y84" s="7" t="n"/>
+      <c r="X84" s="8" t="inlineStr">
+        <is>
+          <t>10826766</t>
+        </is>
+      </c>
+      <c r="Y84" s="8" t="inlineStr">
+        <is>
+          <t>04.05.2031</t>
+        </is>
+      </c>
       <c r="Z84" s="7" t="n"/>
       <c r="AA84" s="9" t="n"/>
       <c r="AB84" s="10">
@@ -10084,7 +10700,7 @@
       <c r="U85" s="7" t="n"/>
       <c r="V85" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЛД Прайд» (ИНН 7449114775)</t>
         </is>
       </c>
       <c r="W85" s="8" t="inlineStr">
@@ -10092,8 +10708,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X85" s="7" t="n"/>
-      <c r="Y85" s="7" t="n"/>
+      <c r="X85" s="8" t="inlineStr">
+        <is>
+          <t>10826766</t>
+        </is>
+      </c>
+      <c r="Y85" s="8" t="inlineStr">
+        <is>
+          <t>04.05.2031</t>
+        </is>
+      </c>
       <c r="Z85" s="7" t="n"/>
       <c r="AA85" s="9" t="n"/>
       <c r="AB85" s="10">
@@ -10204,7 +10828,7 @@
       <c r="U86" s="7" t="n"/>
       <c r="V86" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЛД Прайд» (ИНН 7449114775)</t>
         </is>
       </c>
       <c r="W86" s="8" t="inlineStr">
@@ -10212,8 +10836,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X86" s="7" t="n"/>
-      <c r="Y86" s="7" t="n"/>
+      <c r="X86" s="8" t="inlineStr">
+        <is>
+          <t>10826766</t>
+        </is>
+      </c>
+      <c r="Y86" s="8" t="inlineStr">
+        <is>
+          <t>04.05.2031</t>
+        </is>
+      </c>
       <c r="Z86" s="7" t="n"/>
       <c r="AA86" s="9" t="n"/>
       <c r="AB86" s="10">
@@ -10324,7 +10956,7 @@
       <c r="U87" s="7" t="n"/>
       <c r="V87" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W87" s="8" t="inlineStr">
@@ -10332,8 +10964,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X87" s="7" t="n"/>
-      <c r="Y87" s="7" t="n"/>
+      <c r="X87" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y87" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z87" s="7" t="n"/>
       <c r="AA87" s="9" t="n"/>
       <c r="AB87" s="10">
@@ -10444,7 +11084,7 @@
       <c r="U88" s="7" t="n"/>
       <c r="V88" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W88" s="8" t="inlineStr">
@@ -10452,8 +11092,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X88" s="7" t="n"/>
-      <c r="Y88" s="7" t="n"/>
+      <c r="X88" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y88" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z88" s="7" t="n"/>
       <c r="AA88" s="9" t="n"/>
       <c r="AB88" s="10">
@@ -10564,7 +11212,7 @@
       <c r="U89" s="7" t="n"/>
       <c r="V89" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W89" s="8" t="inlineStr">
@@ -10572,8 +11220,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X89" s="7" t="n"/>
-      <c r="Y89" s="7" t="n"/>
+      <c r="X89" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y89" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z89" s="7" t="n"/>
       <c r="AA89" s="9" t="n"/>
       <c r="AB89" s="10">
@@ -10684,7 +11340,7 @@
       <c r="U90" s="7" t="n"/>
       <c r="V90" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W90" s="8" t="inlineStr">
@@ -10692,8 +11348,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X90" s="7" t="n"/>
-      <c r="Y90" s="7" t="n"/>
+      <c r="X90" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y90" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z90" s="7" t="n"/>
       <c r="AA90" s="9" t="n"/>
       <c r="AB90" s="10">
@@ -10804,7 +11468,7 @@
       <c r="U91" s="7" t="n"/>
       <c r="V91" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W91" s="8" t="inlineStr">
@@ -10812,8 +11476,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X91" s="7" t="n"/>
-      <c r="Y91" s="7" t="n"/>
+      <c r="X91" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y91" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z91" s="7" t="n"/>
       <c r="AA91" s="9" t="n"/>
       <c r="AB91" s="10">
@@ -10924,7 +11596,7 @@
       <c r="U92" s="7" t="n"/>
       <c r="V92" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W92" s="8" t="inlineStr">
@@ -10932,8 +11604,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X92" s="7" t="n"/>
-      <c r="Y92" s="7" t="n"/>
+      <c r="X92" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y92" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z92" s="7" t="n"/>
       <c r="AA92" s="9" t="n"/>
       <c r="AB92" s="10">
@@ -11046,7 +11726,7 @@
       <c r="U93" s="7" t="n"/>
       <c r="V93" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W93" s="8" t="inlineStr">
@@ -11054,8 +11734,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X93" s="7" t="n"/>
-      <c r="Y93" s="7" t="n"/>
+      <c r="X93" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y93" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z93" s="7" t="n"/>
       <c r="AA93" s="9" t="n"/>
       <c r="AB93" s="10">
@@ -11168,7 +11856,7 @@
       <c r="U94" s="7" t="n"/>
       <c r="V94" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W94" s="8" t="inlineStr">
@@ -11176,8 +11864,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X94" s="7" t="n"/>
-      <c r="Y94" s="7" t="n"/>
+      <c r="X94" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y94" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z94" s="7" t="n"/>
       <c r="AA94" s="9" t="n"/>
       <c r="AB94" s="10">
@@ -11290,7 +11986,7 @@
       <c r="U95" s="7" t="n"/>
       <c r="V95" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W95" s="8" t="inlineStr">
@@ -11298,8 +11994,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X95" s="7" t="n"/>
-      <c r="Y95" s="7" t="n"/>
+      <c r="X95" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y95" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z95" s="7" t="n"/>
       <c r="AA95" s="9" t="n"/>
       <c r="AB95" s="10">
@@ -11412,7 +12116,7 @@
       <c r="U96" s="7" t="n"/>
       <c r="V96" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W96" s="8" t="inlineStr">
@@ -11420,8 +12124,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X96" s="7" t="n"/>
-      <c r="Y96" s="7" t="n"/>
+      <c r="X96" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y96" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z96" s="7" t="n"/>
       <c r="AA96" s="9" t="n"/>
       <c r="AB96" s="10">
@@ -11534,7 +12246,7 @@
       <c r="U97" s="7" t="n"/>
       <c r="V97" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W97" s="8" t="inlineStr">
@@ -11542,8 +12254,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X97" s="7" t="n"/>
-      <c r="Y97" s="7" t="n"/>
+      <c r="X97" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y97" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z97" s="7" t="n"/>
       <c r="AA97" s="9" t="n"/>
       <c r="AB97" s="10">
@@ -11654,7 +12374,7 @@
       <c r="U98" s="7" t="n"/>
       <c r="V98" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W98" s="8" t="inlineStr">
@@ -11662,8 +12382,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X98" s="7" t="n"/>
-      <c r="Y98" s="7" t="n"/>
+      <c r="X98" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y98" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z98" s="7" t="n"/>
       <c r="AA98" s="9" t="n"/>
       <c r="AB98" s="10">
@@ -11774,7 +12502,7 @@
       <c r="U99" s="7" t="n"/>
       <c r="V99" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W99" s="8" t="inlineStr">
@@ -11782,8 +12510,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X99" s="7" t="n"/>
-      <c r="Y99" s="7" t="n"/>
+      <c r="X99" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y99" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z99" s="7" t="n"/>
       <c r="AA99" s="9" t="n"/>
       <c r="AB99" s="10">
@@ -11894,7 +12630,7 @@
       <c r="U100" s="7" t="n"/>
       <c r="V100" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W100" s="8" t="inlineStr">
@@ -11902,8 +12638,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X100" s="7" t="n"/>
-      <c r="Y100" s="7" t="n"/>
+      <c r="X100" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y100" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z100" s="7" t="n"/>
       <c r="AA100" s="9" t="n"/>
       <c r="AB100" s="10">
@@ -12017,7 +12761,7 @@
       <c r="U101" s="7" t="n"/>
       <c r="V101" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W101" s="8" t="inlineStr">
@@ -12025,8 +12769,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X101" s="7" t="n"/>
-      <c r="Y101" s="7" t="n"/>
+      <c r="X101" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y101" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z101" s="7" t="n"/>
       <c r="AA101" s="9" t="n"/>
       <c r="AB101" s="10">
@@ -12140,7 +12892,7 @@
       <c r="U102" s="7" t="n"/>
       <c r="V102" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W102" s="8" t="inlineStr">
@@ -12148,8 +12900,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X102" s="7" t="n"/>
-      <c r="Y102" s="7" t="n"/>
+      <c r="X102" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y102" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z102" s="7" t="n"/>
       <c r="AA102" s="9" t="n"/>
       <c r="AB102" s="10">
@@ -12263,7 +13023,7 @@
       <c r="U103" s="7" t="n"/>
       <c r="V103" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W103" s="8" t="inlineStr">
@@ -12271,8 +13031,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X103" s="7" t="n"/>
-      <c r="Y103" s="7" t="n"/>
+      <c r="X103" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y103" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z103" s="7" t="n"/>
       <c r="AA103" s="9" t="n"/>
       <c r="AB103" s="10">
@@ -12386,7 +13154,7 @@
       <c r="U104" s="7" t="n"/>
       <c r="V104" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W104" s="8" t="inlineStr">
@@ -12394,8 +13162,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X104" s="7" t="n"/>
-      <c r="Y104" s="7" t="n"/>
+      <c r="X104" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y104" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z104" s="7" t="n"/>
       <c r="AA104" s="9" t="n"/>
       <c r="AB104" s="10">
@@ -12509,7 +13285,7 @@
       <c r="U105" s="7" t="n"/>
       <c r="V105" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W105" s="8" t="inlineStr">
@@ -12517,8 +13293,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X105" s="7" t="n"/>
-      <c r="Y105" s="7" t="n"/>
+      <c r="X105" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y105" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z105" s="7" t="n"/>
       <c r="AA105" s="9" t="n"/>
       <c r="AB105" s="10">
@@ -12632,7 +13416,7 @@
       <c r="U106" s="7" t="n"/>
       <c r="V106" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W106" s="8" t="inlineStr">
@@ -12640,8 +13424,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X106" s="7" t="n"/>
-      <c r="Y106" s="7" t="n"/>
+      <c r="X106" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y106" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z106" s="7" t="n"/>
       <c r="AA106" s="9" t="n"/>
       <c r="AB106" s="10">
@@ -12759,7 +13551,7 @@
       <c r="U107" s="7" t="n"/>
       <c r="V107" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W107" s="8" t="inlineStr">
@@ -12767,8 +13559,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X107" s="7" t="n"/>
-      <c r="Y107" s="7" t="n"/>
+      <c r="X107" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y107" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z107" s="7" t="n"/>
       <c r="AA107" s="9" t="n"/>
       <c r="AB107" s="10">
@@ -12886,7 +13686,7 @@
       <c r="U108" s="7" t="n"/>
       <c r="V108" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W108" s="8" t="inlineStr">
@@ -12894,8 +13694,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X108" s="7" t="n"/>
-      <c r="Y108" s="7" t="n"/>
+      <c r="X108" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y108" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z108" s="7" t="n"/>
       <c r="AA108" s="9" t="n"/>
       <c r="AB108" s="10">
@@ -13013,7 +13821,7 @@
       <c r="U109" s="7" t="n"/>
       <c r="V109" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W109" s="8" t="inlineStr">
@@ -13021,8 +13829,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X109" s="7" t="n"/>
-      <c r="Y109" s="7" t="n"/>
+      <c r="X109" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y109" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z109" s="7" t="n"/>
       <c r="AA109" s="9" t="n"/>
       <c r="AB109" s="10">
@@ -13140,7 +13956,7 @@
       <c r="U110" s="7" t="n"/>
       <c r="V110" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W110" s="8" t="inlineStr">
@@ -13148,8 +13964,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X110" s="7" t="n"/>
-      <c r="Y110" s="7" t="n"/>
+      <c r="X110" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y110" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z110" s="7" t="n"/>
       <c r="AA110" s="9" t="n"/>
       <c r="AB110" s="10">
@@ -13259,7 +14083,7 @@
       <c r="U111" s="7" t="n"/>
       <c r="V111" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W111" s="8" t="inlineStr">
@@ -13267,8 +14091,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X111" s="7" t="n"/>
-      <c r="Y111" s="7" t="n"/>
+      <c r="X111" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y111" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z111" s="7" t="n"/>
       <c r="AA111" s="9" t="n"/>
       <c r="AB111" s="10">
@@ -13486,7 +14318,7 @@
       <c r="U113" s="7" t="n"/>
       <c r="V113" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W113" s="8" t="inlineStr">
@@ -13494,8 +14326,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X113" s="7" t="n"/>
-      <c r="Y113" s="7" t="n"/>
+      <c r="X113" s="8" t="inlineStr">
+        <is>
+          <t>10714005</t>
+        </is>
+      </c>
+      <c r="Y113" s="8" t="inlineStr">
+        <is>
+          <t>17.09.2028</t>
+        </is>
+      </c>
       <c r="Z113" s="7" t="n"/>
       <c r="AA113" s="9" t="n"/>
       <c r="AB113" s="10">
@@ -13601,7 +14441,7 @@
       <c r="U114" s="7" t="n"/>
       <c r="V114" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W114" s="8" t="inlineStr">
@@ -13609,8 +14449,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X114" s="7" t="n"/>
-      <c r="Y114" s="7" t="n"/>
+      <c r="X114" s="8" t="inlineStr">
+        <is>
+          <t>10714005</t>
+        </is>
+      </c>
+      <c r="Y114" s="8" t="inlineStr">
+        <is>
+          <t>17.09.2028</t>
+        </is>
+      </c>
       <c r="Z114" s="7" t="n"/>
       <c r="AA114" s="9" t="n"/>
       <c r="AB114" s="10">
@@ -13716,7 +14564,7 @@
       <c r="U115" s="7" t="n"/>
       <c r="V115" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W115" s="8" t="inlineStr">
@@ -13724,8 +14572,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X115" s="7" t="n"/>
-      <c r="Y115" s="7" t="n"/>
+      <c r="X115" s="8" t="inlineStr">
+        <is>
+          <t>10714005</t>
+        </is>
+      </c>
+      <c r="Y115" s="8" t="inlineStr">
+        <is>
+          <t>17.09.2028</t>
+        </is>
+      </c>
       <c r="Z115" s="7" t="n"/>
       <c r="AA115" s="9" t="n"/>
       <c r="AB115" s="10">
@@ -13831,7 +14687,7 @@
       <c r="U116" s="7" t="n"/>
       <c r="V116" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W116" s="8" t="inlineStr">
@@ -13839,8 +14695,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X116" s="7" t="n"/>
-      <c r="Y116" s="7" t="n"/>
+      <c r="X116" s="8" t="inlineStr">
+        <is>
+          <t>10714005</t>
+        </is>
+      </c>
+      <c r="Y116" s="8" t="inlineStr">
+        <is>
+          <t>17.09.2028</t>
+        </is>
+      </c>
       <c r="Z116" s="7" t="n"/>
       <c r="AA116" s="9" t="n"/>
       <c r="AB116" s="10">
@@ -13946,7 +14810,7 @@
       <c r="U117" s="7" t="n"/>
       <c r="V117" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W117" s="8" t="inlineStr">
@@ -13954,8 +14818,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X117" s="7" t="n"/>
-      <c r="Y117" s="7" t="n"/>
+      <c r="X117" s="8" t="inlineStr">
+        <is>
+          <t>10714005</t>
+        </is>
+      </c>
+      <c r="Y117" s="8" t="inlineStr">
+        <is>
+          <t>17.09.2028</t>
+        </is>
+      </c>
       <c r="Z117" s="7" t="n"/>
       <c r="AA117" s="9" t="n"/>
       <c r="AB117" s="10">
@@ -14061,7 +14933,7 @@
       <c r="U118" s="7" t="n"/>
       <c r="V118" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W118" s="8" t="inlineStr">
@@ -14069,8 +14941,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X118" s="7" t="n"/>
-      <c r="Y118" s="7" t="n"/>
+      <c r="X118" s="8" t="inlineStr">
+        <is>
+          <t>10714005</t>
+        </is>
+      </c>
+      <c r="Y118" s="8" t="inlineStr">
+        <is>
+          <t>17.09.2028</t>
+        </is>
+      </c>
       <c r="Z118" s="7" t="n"/>
       <c r="AA118" s="9" t="n"/>
       <c r="AB118" s="10">
@@ -14181,7 +15061,7 @@
       <c r="U119" s="7" t="n"/>
       <c r="V119" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W119" s="8" t="inlineStr">
@@ -14189,8 +15069,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X119" s="7" t="n"/>
-      <c r="Y119" s="7" t="n"/>
+      <c r="X119" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y119" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z119" s="7" t="n"/>
       <c r="AA119" s="9" t="n"/>
       <c r="AB119" s="10">
@@ -14301,7 +15189,7 @@
       <c r="U120" s="7" t="n"/>
       <c r="V120" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W120" s="8" t="inlineStr">
@@ -14309,8 +15197,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X120" s="7" t="n"/>
-      <c r="Y120" s="7" t="n"/>
+      <c r="X120" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y120" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z120" s="7" t="n"/>
       <c r="AA120" s="9" t="n"/>
       <c r="AB120" s="10">
@@ -14421,7 +15317,7 @@
       <c r="U121" s="7" t="n"/>
       <c r="V121" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W121" s="8" t="inlineStr">
@@ -14429,8 +15325,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X121" s="7" t="n"/>
-      <c r="Y121" s="7" t="n"/>
+      <c r="X121" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y121" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z121" s="7" t="n"/>
       <c r="AA121" s="9" t="n"/>
       <c r="AB121" s="10">
@@ -14533,7 +15437,7 @@
       <c r="U122" s="7" t="n"/>
       <c r="V122" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W122" s="8" t="inlineStr">
@@ -14541,8 +15445,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X122" s="7" t="n"/>
-      <c r="Y122" s="7" t="n"/>
+      <c r="X122" s="8" t="inlineStr">
+        <is>
+          <t>10657717</t>
+        </is>
+      </c>
+      <c r="Y122" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z122" s="7" t="n"/>
       <c r="AA122" s="9" t="n"/>
       <c r="AB122" s="10">
@@ -14645,7 +15557,7 @@
       <c r="U123" s="7" t="n"/>
       <c r="V123" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W123" s="8" t="inlineStr">
@@ -14653,8 +15565,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X123" s="7" t="n"/>
-      <c r="Y123" s="7" t="n"/>
+      <c r="X123" s="8" t="inlineStr">
+        <is>
+          <t>10657717</t>
+        </is>
+      </c>
+      <c r="Y123" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z123" s="7" t="n"/>
       <c r="AA123" s="9" t="n"/>
       <c r="AB123" s="10">
@@ -14757,7 +15677,7 @@
       <c r="U124" s="7" t="n"/>
       <c r="V124" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W124" s="8" t="inlineStr">
@@ -14765,8 +15685,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X124" s="7" t="n"/>
-      <c r="Y124" s="7" t="n"/>
+      <c r="X124" s="8" t="inlineStr">
+        <is>
+          <t>10657717</t>
+        </is>
+      </c>
+      <c r="Y124" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z124" s="7" t="n"/>
       <c r="AA124" s="9" t="n"/>
       <c r="AB124" s="10">
@@ -14869,7 +15797,7 @@
       <c r="U125" s="7" t="n"/>
       <c r="V125" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W125" s="8" t="inlineStr">
@@ -14877,8 +15805,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X125" s="7" t="n"/>
-      <c r="Y125" s="7" t="n"/>
+      <c r="X125" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y125" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z125" s="7" t="n"/>
       <c r="AA125" s="9" t="n"/>
       <c r="AB125" s="10">
@@ -14981,7 +15917,7 @@
       <c r="U126" s="7" t="n"/>
       <c r="V126" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W126" s="8" t="inlineStr">
@@ -14989,8 +15925,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X126" s="7" t="n"/>
-      <c r="Y126" s="7" t="n"/>
+      <c r="X126" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y126" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z126" s="7" t="n"/>
       <c r="AA126" s="9" t="n"/>
       <c r="AB126" s="10">
@@ -15093,7 +16037,7 @@
       <c r="U127" s="7" t="n"/>
       <c r="V127" s="8" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
         </is>
       </c>
       <c r="W127" s="8" t="inlineStr">
@@ -15101,8 +16045,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X127" s="7" t="n"/>
-      <c r="Y127" s="7" t="n"/>
+      <c r="X127" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="Y127" s="8" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="Z127" s="7" t="n"/>
       <c r="AA127" s="9" t="n"/>
       <c r="AB127" s="10">
